--- a/AAII_Financials/Quarterly/TMO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>TMO</t>
   </si>
@@ -656,539 +656,551 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11994000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11005000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12215000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11122000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10855000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10364000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11395000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10598000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10541000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10345000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10886000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10574000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10687000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10710000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11450000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10677000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10970000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11818000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10702000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28509000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9273000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9906000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10550000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8521000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6917000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6230000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6829000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6272000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6316000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6125000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6507000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5920000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6078000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5853000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6046800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5116200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4990000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4765000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4953200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4490900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7084000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6561000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7171000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6529000</v>
       </c>
-      <c r="G9" s="3">
-        <v>6441000</v>
-      </c>
       <c r="H9" s="3">
+        <v>6436000</v>
+      </c>
+      <c r="I9" s="3">
         <v>6118000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6551000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6261000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6194000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6125000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6471000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6244000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6418000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6529000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6844000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6375000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6371000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6354000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5448000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14125000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4749000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4697000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4994000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4190000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3540000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3490000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3794000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3509000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3493000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3418000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3583000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3305000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3340000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3273000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3377600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2816000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2706900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2572500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2674400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2437000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4910000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4444000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5044000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4593000</v>
       </c>
-      <c r="G10" s="3">
-        <v>4414000</v>
-      </c>
       <c r="H10" s="3">
+        <v>4419000</v>
+      </c>
+      <c r="I10" s="3">
         <v>4246000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4844000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4337000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4347000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4220000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4415000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4330000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4269000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4181000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4606000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4302000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4599000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5464000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5254000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14384000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4524000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5209000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5556000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4331000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3377000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2740000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3035000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2763000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2823000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2707000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2924000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2615000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2738000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2580000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2669200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2300200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2283100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2192500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2278800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2053900</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,130 +1243,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E12" s="3">
         <v>336000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>356000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>346000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>352000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>342000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>374000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>346000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>339000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>331000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>327000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>319000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>345000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>346000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>391000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>351000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>365000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>364000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>392000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1014000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>343000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>320000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>376000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>296000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>264000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>245000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>262000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>247000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>246000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>248000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>251000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>240000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>242000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>234000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>232900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>218100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>221600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>215400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>212600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1475,175 +1491,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E14" s="3">
         <v>106000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>315000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>203000</v>
       </c>
-      <c r="G14" s="3">
-        <v>110000</v>
-      </c>
       <c r="H14" s="3">
+        <v>115000</v>
+      </c>
+      <c r="I14" s="3">
         <v>122000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>222000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>79000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>52000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>145000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>101000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>207000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>205000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>55000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>33000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>24000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>727000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>210000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>77000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>227000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>29000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>54000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>44000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>37000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>38000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-448000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>11000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>37000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-31000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>53000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>5200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>85500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>29300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>55000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>57000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>117400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E15" s="3">
         <v>734000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>728000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>671000</v>
       </c>
-      <c r="G15" s="3">
-        <v>676000</v>
-      </c>
       <c r="H15" s="3">
+        <v>686000</v>
+      </c>
+      <c r="I15" s="3">
         <v>705000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>742000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>750000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>780000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>836000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>839000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>853000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>855000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>859000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1741,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1785,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>9745000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9036000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9629000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8978000</v>
       </c>
-      <c r="G17" s="3">
-        <v>8918000</v>
-      </c>
       <c r="H17" s="3">
+        <v>8908000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8524000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9133000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8686000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8708000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8620000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8895000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8598000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8902000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8986000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9589000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8967000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8969000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9023000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8734000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21019000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7110000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7054000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7479000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6095000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5526000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5324000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5597000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5326000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4820000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5205000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5359000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5008000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5141000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5067000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5088900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4480000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4238500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4142600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4200600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3949800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2249000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1969000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2586000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2144000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1937000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1947000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1840000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2262000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1912000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1833000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1725000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1991000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1976000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1785000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1724000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1861000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1710000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2001000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2795000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1968000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7490000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2163000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2852000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3071000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2426000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1391000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>906000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1232000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>946000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1496000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>920000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1148000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>912000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>786000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>957900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>636200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>751500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>622400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>752600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>541100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2048,618 +2080,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>79000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>26000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>185000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>64000</v>
       </c>
       <c r="S20" s="3">
         <v>64000</v>
       </c>
       <c r="T20" s="3">
+        <v>64000</v>
+      </c>
+      <c r="U20" s="3">
         <v>-119000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>61000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-136000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>26000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>48000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>78000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>86000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>36000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>60000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>11000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>28300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>7700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>15900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>30600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3059000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2687000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3273000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2815000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2604000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2619000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2533000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3028000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2637000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2534000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2585000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2804000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2815000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2625000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2560000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2894000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2612000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2901000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3535000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2712000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9263000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2829000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3499000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3640000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2971000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1964000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1528000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1756000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1561000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2145000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1561000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1742000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1535000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1547000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1372000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1559700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1154100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1237400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1102800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1257000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>974200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E22" s="3">
         <v>354000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>365000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>347000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>404000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>303000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>317000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>356000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>354000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>363000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>390000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>359000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>327000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>304000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>269000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>173000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>148000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>136000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>161000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>375000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>122000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>125000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>146000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>144000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>137000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>126000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>142000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>164000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>181000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>189000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>172000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>162000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>170000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>163000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>166300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>156700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>133600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>135400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>131300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>113300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1908000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1726000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2123000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1828000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1711000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1606000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1974000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1729000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1682000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1613000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1739000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1748000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1414000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1338000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1777000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1601000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1917000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2540000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1868000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6979000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2047000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2753000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2892000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2252000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1253000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>828000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1038000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>822000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1393000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>817000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>810000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>634000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>819900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>480600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>625600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>502900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>651900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>427900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E24" s="3">
         <v>70000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>153000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>207000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>92000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>95000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>150000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>128000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>281000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>133000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>53000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>52000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>173000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>31000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>198000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>301000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>203000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>906000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>219000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>416000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>394000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>319000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>97000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>36000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>274000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>22000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>114000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>54000</v>
       </c>
       <c r="AI24" s="3">
         <v>54000</v>
       </c>
       <c r="AJ24" s="3">
+        <v>54000</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>85400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-53300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>13400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-48500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>19200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-45600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2780,252 +2828,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1741000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1656000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1970000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1621000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1619000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1511000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1824000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1630000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1554000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1332000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1606000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1695000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1362000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1292000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1604000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1570000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1719000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2239000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1665000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6073000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1828000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2337000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>788000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>788000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>795000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>898000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>756000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>752000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>649000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>734500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>533900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>612200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>551400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>632700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>473500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1651000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1964000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1616000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1617000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1507000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1830000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1630000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1548000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1328000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1630000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1715000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1361000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1289000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1576000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1495000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1664000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2215000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1658000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6067000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1828000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2337000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>788000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>788000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>795000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>898000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>756000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>752000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>649000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>734500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>533900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>612200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>551400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>632700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>473500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3146,8 +3203,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3211,8 +3271,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>91</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>91</v>
@@ -3223,53 +3283,56 @@
       <c r="AA29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>20000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-47000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-70000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-206400</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-600</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
       <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3390,8 +3453,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3512,252 +3578,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-79000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-26000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-185000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-64000</v>
       </c>
       <c r="S32" s="3">
         <v>-64000</v>
       </c>
       <c r="T32" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="U32" s="3">
         <v>119000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-61000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>136000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>33000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>30000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>52000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-78000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-86000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-60000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-28300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1651000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1964000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1616000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1617000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1507000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1830000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1630000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1548000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1328000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1630000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1715000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1361000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1289000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1576000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1495000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1664000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2215000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1658000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6067000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1828000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2337000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>788000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>760000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>815000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>898000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>709000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>752000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>579000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>528100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>533900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>611600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>551400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>629500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>473500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3878,257 +3953,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1651000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1964000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1616000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1617000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1507000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1830000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1630000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1548000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1328000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1630000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1715000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1361000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1289000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1576000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1495000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1664000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2215000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1658000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6067000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1828000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2337000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>788000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>760000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>815000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>898000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>709000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>752000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>579000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>528100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>533900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>611600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>551400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>629500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>473500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4171,8 +4255,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4215,796 +4300,815 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4064000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3254000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9852000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1982000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4576000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4134000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4009000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4645000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7073000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5499000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8077000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6151000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3133000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3482000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8524000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2919000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1888000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2752000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4477000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12027000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7023000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5583000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10325000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7540000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5818000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2981000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2399000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1273000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2288000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1106000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2103000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1098000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>950000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1335000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>741100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>611000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>713300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>786200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1970000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>253000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1564000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1814000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1813000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1561000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2000000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1750000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1751000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>22000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6000</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X42" s="3">
         <v>65000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>121000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>28000</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC42" s="3">
         <v>110000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>37000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>9000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>31000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>14000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>7300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>53500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>11600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>15800</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>11139000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10888000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10566000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10531000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10035000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9821000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9626000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9796000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9430000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9353000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9664000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9835000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9486000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9297000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9427000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8919000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8892000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8947000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8945000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6365000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6280000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6337000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6472000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5883000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5164000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5166000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4952000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4384000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4129000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4155000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4136000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4257000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4441000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4530000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4311000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4209100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3673200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3523500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3426800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2895100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>5627000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5496000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5425000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5745000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5559000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5224000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4978000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5430000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5198000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5133000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5088000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5404000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5655000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5664000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5634000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5722000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5668000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5483000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5051000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4906000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4625000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4342000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4029000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3829000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3648000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3454000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3370000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3308000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3209000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3124000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3005000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2982000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2866000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2891000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2971000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3125500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2422200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2327100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2213300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2390900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>2524000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2672000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2606000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2466000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2597000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2370000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1953000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1901000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2014000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1897000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1751000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1690000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1708000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1755000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1644000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1717000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1647000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1588000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1640000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1426000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1267000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1302000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1103000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>982000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1027000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1135000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1542000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1591000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1545000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1350000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1215000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1227000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1210000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>794000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>761000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>692600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>672600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>578900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>933600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>23365000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22316000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28707000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22295000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24584000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23378000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22137000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23783000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25476000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23640000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24589000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23092000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19995000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20209000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25229000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19299000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18100000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18776000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20113000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24724000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19260000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17685000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21957000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18234000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15775000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12738000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11893000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10514000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11223000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9939000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10625000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9566000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9474000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9588000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9421000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8844000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>7452500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7248100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7021000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>8204400</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3">
         <v>438000</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>174000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>352000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>438000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>478000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>219000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>534000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>87000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11000</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>91</v>
@@ -5015,8 +5119,8 @@
       <c r="X47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -5069,252 +5173,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>10755000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10658000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12012000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10177000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9635000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9331000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10795000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9412000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9282000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9324000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11004000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9167000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9292000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9354000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9280000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8628000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8529000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8448000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9864000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7049000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6560000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6133000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6687000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5180000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4887000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4736000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5448000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5065000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5027000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4792000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4165000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3978000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3952000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4059000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4047000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3931600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2599700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2563300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2577800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2599300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>73438000</v>
+      </c>
+      <c r="E49" s="3">
         <v>74333000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>65200000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>65529000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>62397000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>61816000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>61386000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>62988000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>59362000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>59891000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>60690000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60674000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>60710000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>61112000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>58638000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>58301000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>59644000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>61099000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>62037000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>38836000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>39294000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>39654000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>38726000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>38652000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38870000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>39157000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39728000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39935000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40620000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>39725000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>40325000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>40361000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>40800000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>41755000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>41974000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>42158500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>35421100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>35382000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>35296800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>36102400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5435,8 +5548,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5557,130 +5673,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>5616000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5974000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3985000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5019000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4440000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4164000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2559000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4082000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3891000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4012000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1905000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4032000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4096000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3925000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4000000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4299000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4296000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4413000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3109000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2991000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2584000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2459000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1682000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1995000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2061000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2057000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1312000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1215000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1100000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1140000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1117000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1173000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1177000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1178000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1227000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1051200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1040400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1020200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1011900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1104600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5801,130 +5923,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>113174000</v>
+      </c>
+      <c r="E54" s="3">
         <v>113281000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110343000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>103020000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101230000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>99041000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97321000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100364000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>98496000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97095000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>98726000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97057000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94105000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94658000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97154000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>90536000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>90579000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>92747000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>95123000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>73600000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67698000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65931000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>69052000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64061000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>61593000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>58688000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>58381000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56729000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>57970000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55596000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56232000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55078000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55403000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56580000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>56669000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>55985300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>46513700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>46213600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>45907500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>48010700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5967,8 +6095,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6011,740 +6140,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3268000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3344000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3622000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3120000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2980000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3049000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3079000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2606000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2547000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2555000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2872000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2508000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2423000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2798000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3381000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2471000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2586000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2667000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2867000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2301000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2098000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2146000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2175000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1703000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1385000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1599000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1920000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1659000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1391000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1462000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1615000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1344000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1359000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1354000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1428000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1123800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>982200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1031000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>926200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>941700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3368000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3090000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3808000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3823000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2214000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2819000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2475000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4116000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5121000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4451000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3872000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4795000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4814000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6122000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5579000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1010000</v>
       </c>
       <c r="S58" s="3">
         <v>1010000</v>
       </c>
       <c r="T58" s="3">
+        <v>1010000</v>
+      </c>
+      <c r="U58" s="3">
         <v>1866000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2537000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>19000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>4000</v>
       </c>
       <c r="X58" s="3">
         <v>4000</v>
       </c>
       <c r="Y58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>2628000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>675000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>738000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>676000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>661000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2377000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1336000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1271000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1014000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1711000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2814000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2135000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2762300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1540400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1882400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1255500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1972100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2989000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2994000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2782000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2938000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2882000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2926000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2904000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2718000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2640000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2684000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2749000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2621000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2689000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2718000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8050000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7637000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7401000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7537000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8032000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5433000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4823000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4845000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5501000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4523000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3953000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3163000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3601000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3524000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3741000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3100000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3261000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2838000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2910000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2904000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3485000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3145200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2553200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2389500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2684100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2346100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>15069000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14621000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15189000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14888000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12718000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13174000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13332000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14601000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14772000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13937000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14012000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14158000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14112000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15884000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17010000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11118000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10997000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12070000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13436000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7753000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6925000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6995000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10304000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6228000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6013000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5500000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6197000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5844000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7509000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5898000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6147000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5196000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5980000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7072000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7048000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7031300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5075800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5302900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4865800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>5259900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>39181000</v>
+      </c>
+      <c r="E61" s="3">
         <v>40071000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37047000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31857000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33015000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31440000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30300000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31397000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30306000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31213000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>32839000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30641000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29209000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29214000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28909000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28150000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29250000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30095000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32333000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21688000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18773000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18641000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19107000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21091000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20638000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>19231000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17076000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16392000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16663000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16812000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>17719000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>17760000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17709000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18122000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>18873000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19230400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15255700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>15188400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>15372400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>16940400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>4538000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4420000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1513000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4279000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4270000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3901000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1257000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2716000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2912000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3084000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1229000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2826000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2929000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2979000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7087000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7541000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7861000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9451000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8377000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5449000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5146000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5237000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5134000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4918000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5067000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5398000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5433000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5138000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5069000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5193000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4780000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5232000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5269000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5263000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5335000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5021800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3790600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3927100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>4130000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>4151800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6865,8 +7013,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6987,8 +7138,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7109,130 +7263,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>60367000</v>
+      </c>
+      <c r="E66" s="3">
         <v>61219000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56807000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51866000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50627000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>49556000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47650000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51265000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50961000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51472000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51884000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51593000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>50190000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52225000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53176000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>46987000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48286000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51791000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54330000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34890000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30844000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30873000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34545000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32237000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31718000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>30129000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28706000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>27374000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>29241000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>27903000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28646000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28188000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>28958000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>30457000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>31256000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>31283500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>24122100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>24418400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>24368200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>26352100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7275,8 +7435,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7397,8 +7558,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7519,8 +7683,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7641,8 +7808,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7763,130 +7933,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>62194000</v>
+      </c>
+      <c r="E72" s="3">
         <v>60632000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59156000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>57354000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55901000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54447000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53102000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51421000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49940000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48542000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47364000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45869000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44289000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43064000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41910000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>40452000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>39074000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37528000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35431000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33876000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>32076000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30350000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28116000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25705000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>23860000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22791000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22092000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21165000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20482000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19439000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18696000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17866000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17226000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16542000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15914000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>15445800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14972300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14419400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13926900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>13356500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8007,8 +8183,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8129,8 +8308,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8251,130 +8433,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>52679000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51934000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53407000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51018000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50512000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49390000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49584000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48992000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47432000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45516000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46735000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45328000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43752000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42257000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43978000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>43549000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>42293000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40956000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>40793000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38710000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>36854000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35058000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>34507000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31824000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29875000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28559000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29675000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29355000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28729000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27693000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27586000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>26890000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>26445000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>26123000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25413000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>24701800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>22391600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>21795200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>21539300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>21658600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8495,257 +8683,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1651000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1964000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1616000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1617000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1507000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1830000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1630000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1548000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1328000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1630000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1715000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1361000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1289000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1576000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1495000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1664000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2215000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1658000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6067000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1828000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2337000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1156000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>788000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>760000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>815000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>898000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>709000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>752000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>579000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>528100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>533900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>611600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>551400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>629500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>473500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8788,130 +8985,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E83" s="3">
         <v>276000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>304000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>301000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>266000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>285000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>276000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>269000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>270000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>253000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>256000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>244000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>236000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>250000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>848000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>838000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>836000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>859000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>683000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1909000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>660000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>621000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>602000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>575000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>574000</v>
       </c>
       <c r="AB83" s="3">
         <v>574000</v>
       </c>
       <c r="AC83" s="3">
+        <v>574000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>576000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>575000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>571000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>555000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>558000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>563000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>571000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>575000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>573500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>516800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>478200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>464500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>473800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>433000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9032,8 +9233,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9154,8 +9358,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9276,8 +9483,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9398,8 +9608,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9520,130 +9733,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1192000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3457000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2239000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1399000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>723000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3290000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2166000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1960000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1251000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3723000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2414000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1540000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>729000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3487000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1937000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1528000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2202000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2457000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6855000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2227000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1978000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3339000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2708000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1886000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>356000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1913000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1294000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>649000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1801000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1220000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1444000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>78000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1866500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>928600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>848400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>361500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1103600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>804400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9686,130 +9905,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-450000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-376000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-465000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-404000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-294000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-362000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-480000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-272000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-301000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-347000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-405000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-332000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-284000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-458000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-550000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-547000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-506000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-640000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-831000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-524000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-540000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-628000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-586000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-366000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-269000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-253000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-289000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-216000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-220000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-201000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-183000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-118000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-215200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-111400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-88000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-93400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>177400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-162000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9930,8 +10153,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10052,130 +10278,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8961000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>891000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4123000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-288000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-527000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3578000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-253000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2030000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-376000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1181000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-443000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3142000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-525000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-545000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-419000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-670000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18692000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3240000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-626000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1998000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-626000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-259000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-339000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-198000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-769000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-181000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-721000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-168000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-185000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-179000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-283400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-6968300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-95400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-381900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-104200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-4192600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10218,73 +10450,74 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>162000</v>
+        <v>175000</v>
       </c>
       <c r="E96" s="3">
         <v>162000</v>
       </c>
       <c r="F96" s="3">
+        <v>162000</v>
+      </c>
+      <c r="G96" s="3">
         <v>163000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>162000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>149000</v>
       </c>
       <c r="I96" s="3">
         <v>149000</v>
       </c>
       <c r="J96" s="3">
+        <v>149000</v>
+      </c>
+      <c r="K96" s="3">
         <v>150000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>149000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>135000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>136000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>135000</v>
       </c>
       <c r="O96" s="3">
         <v>135000</v>
       </c>
       <c r="P96" s="3">
+        <v>135000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>117000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-117000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-118000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-117000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-103000</v>
       </c>
       <c r="U96" s="3">
         <v>-103000</v>
       </c>
       <c r="V96" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-292000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-103000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-87000</v>
       </c>
       <c r="Y96" s="3">
         <v>-87000</v>
@@ -10296,52 +10529,55 @@
         <v>-87000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-76000</v>
+        <v>-87000</v>
       </c>
       <c r="AC96" s="3">
         <v>-76000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-77000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-68000</v>
       </c>
       <c r="AG96" s="3">
         <v>-68000</v>
       </c>
       <c r="AH96" s="3">
-        <v>-69000</v>
+        <v>-68000</v>
       </c>
       <c r="AI96" s="3">
         <v>-69000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-60000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-59900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-59300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-58700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-59100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-59800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10462,8 +10698,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10584,8 +10823,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10706,370 +10948,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1571000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1093000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3526000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-632000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-991000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-102000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3666000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1190000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-115000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1821000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1855000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1456000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2593000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2391000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-151000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1905000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3145000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8467000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1886000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-76000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4850000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-791000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1180000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>619000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-514000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1869000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>690000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1425000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-876000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-342000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1144300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>6080600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-963000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-119300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2191500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>4753300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E101" s="3">
         <v>37000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-273000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>175000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-73000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-31000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>250000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-212000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-78000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>250000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-212000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-78000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-99000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>211000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-93000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>137000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>102000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>181000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>20000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-127000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>57000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-59000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-61000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-272000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>57000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>163900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>87900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>102400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>65800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-110100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6598000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7868000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2591000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>431000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>131000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-629000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2427000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1577000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2578000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1929000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3015000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-347000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5037000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5603000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1029000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-874000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1712000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7557000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1712000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1432000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4733000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2766000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1733000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2827000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>588000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1117000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1009000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1186000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-989000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>155000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-386000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>602700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>128800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-107600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-73900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1199800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1310400</v>
       </c>
     </row>
